--- a/test/owner2.xlsx
+++ b/test/owner2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620C0A08-4193-45C8-92BB-DBE5EE88E4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658A7518-3C65-41C3-AE7C-AE0554D25DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="18900" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>client</t>
   </si>
   <si>
-    <t>owner_name</t>
-  </si>
-  <si>
     <t>share</t>
   </si>
   <si>
@@ -73,16 +70,37 @@
     <t>Daee</t>
   </si>
   <si>
-    <t>John Doe</t>
-  </si>
-  <si>
     <t>john@example.com</t>
   </si>
   <si>
     <t>dae@gmail.com</t>
   </si>
   <si>
-    <t>DFGHJ12334</t>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Ritika</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>user_password</t>
+  </si>
+  <si>
+    <t>John@14</t>
+  </si>
+  <si>
+    <t>Ritika@14</t>
+  </si>
+  <si>
+    <t>DFGHJ1233D</t>
   </si>
 </sst>
 </file>
@@ -122,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -145,17 +163,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -461,89 +493,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>20</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
       </c>
       <c r="F2">
         <v>9876543210</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
       </c>
       <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
         <v>13</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E3">
         <v>123456789901</v>
@@ -552,22 +596,30 @@
         <v>1234567891</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{C862AAFE-952B-4693-BA14-1FE2CD5708A1}"/>
     <hyperlink ref="G2" r:id="rId2" xr:uid="{B0EA249D-3048-433B-866E-06425DC89234}"/>
+    <hyperlink ref="L2" r:id="rId3" xr:uid="{763D3371-E3EC-421F-8594-31EE378AA976}"/>
+    <hyperlink ref="L3" r:id="rId4" xr:uid="{DE3D2428-6950-4C77-94C1-E1B44F88C056}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test/owner2.xlsx
+++ b/test/owner2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658A7518-3C65-41C3-AE7C-AE0554D25DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B46C712-250F-448E-AEB1-A4BD4A7CE06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="18900" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
-    <t>client</t>
-  </si>
-  <si>
     <t>share</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>123456789012</t>
   </si>
   <si>
-    <t>pass1234</t>
-  </si>
-  <si>
     <t>username</t>
   </si>
   <si>
@@ -64,9 +58,6 @@
     <t>Dae</t>
   </si>
   <si>
-    <t>Dae1234</t>
-  </si>
-  <si>
     <t>Daee</t>
   </si>
   <si>
@@ -101,6 +92,15 @@
   </si>
   <si>
     <t>DFGHJ1233D</t>
+  </si>
+  <si>
+    <t>Dae@123</t>
+  </si>
+  <si>
+    <t>john@123</t>
+  </si>
+  <si>
+    <t>client_id</t>
   </si>
 </sst>
 </file>
@@ -185,7 +185,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -502,78 +502,78 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>20</v>
       </c>
       <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
       <c r="F2">
         <v>9876543210</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -581,13 +581,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>123456789901</v>
@@ -596,22 +596,22 @@
         <v>1234567891</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
         <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -620,6 +620,8 @@
     <hyperlink ref="G2" r:id="rId2" xr:uid="{B0EA249D-3048-433B-866E-06425DC89234}"/>
     <hyperlink ref="L2" r:id="rId3" xr:uid="{763D3371-E3EC-421F-8594-31EE378AA976}"/>
     <hyperlink ref="L3" r:id="rId4" xr:uid="{DE3D2428-6950-4C77-94C1-E1B44F88C056}"/>
+    <hyperlink ref="H3" r:id="rId5" xr:uid="{08CD85E3-4EBF-4EB6-9215-6DD27FC855BC}"/>
+    <hyperlink ref="H2" r:id="rId6" xr:uid="{1D5DDE3C-6F16-49B4-9EB4-D7179881236D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test/owner2.xlsx
+++ b/test/owner2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B46C712-250F-448E-AEB1-A4BD4A7CE06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880B8964-15B1-4063-ACD3-65DF69A51E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>share</t>
   </si>
@@ -101,13 +101,19 @@
   </si>
   <si>
     <t>client_id</t>
+  </si>
+  <si>
+    <t>Dae@124</t>
+  </si>
+  <si>
+    <t>Ritika@15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,6 +133,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -493,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
@@ -584,7 +596,7 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -614,7 +626,46 @@
         <v>22</v>
       </c>
     </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>123456789901</v>
+      </c>
+      <c r="F4">
+        <v>1234567891</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{C862AAFE-952B-4693-BA14-1FE2CD5708A1}"/>
     <hyperlink ref="G2" r:id="rId2" xr:uid="{B0EA249D-3048-433B-866E-06425DC89234}"/>
@@ -622,6 +673,9 @@
     <hyperlink ref="L3" r:id="rId4" xr:uid="{DE3D2428-6950-4C77-94C1-E1B44F88C056}"/>
     <hyperlink ref="H3" r:id="rId5" xr:uid="{08CD85E3-4EBF-4EB6-9215-6DD27FC855BC}"/>
     <hyperlink ref="H2" r:id="rId6" xr:uid="{1D5DDE3C-6F16-49B4-9EB4-D7179881236D}"/>
+    <hyperlink ref="G4" r:id="rId7" xr:uid="{714E383B-557C-4DB2-94A9-CC60D5CCFD0D}"/>
+    <hyperlink ref="H4" r:id="rId8" display="Dae@123" xr:uid="{631E8BA1-7880-4802-9F8E-464BF2014085}"/>
+    <hyperlink ref="L4" r:id="rId9" display="Ritika@14" xr:uid="{CD1D9B16-8C9A-4E92-9ECD-DE4059B51B3E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
